--- a/plugins/jan-kapitalfluss/fixtures/liquiditaet/liquiditaet.fixture.xlsx
+++ b/plugins/jan-kapitalfluss/fixtures/liquiditaet/liquiditaet.fixture.xlsx
@@ -11,24 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>Liquiditätsplanung (P&amp;L) — Mai 2026</t>
+    <t>Liquiditätsplanung — Mai 2026</t>
   </si>
   <si>
-    <t>Umsatzerlöse</t>
+    <t>Einnahmen (Summe)</t>
   </si>
   <si>
-    <t>Wareneinkauf</t>
-  </si>
-  <si>
-    <t>Raumkosten</t>
-  </si>
-  <si>
-    <t>Personalkosten</t>
-  </si>
-  <si>
-    <t>Energie</t>
+    <t>Ausgaben (Summe)</t>
   </si>
 </sst>
 </file>
@@ -409,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:C9"/>
+  <dimension ref="B3:C6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.25">
@@ -433,30 +424,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
